--- a/Güncel Stok.xlsx
+++ b/Güncel Stok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA81A855-183F-4284-B15E-6346D34AA7B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A181EAD-6AC9-4083-8BA4-F6C2C27A7744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10952,9 +10952,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet"/>
   <dimension ref="A1:I2076"/>
-  <sheetFormatPr defaultColWidth="18.69921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="21.69921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="18.69921875" style="1"/>
+    <col min="1" max="16384" width="21.69921875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -46496,7 +46496,7 @@
         <v>625</v>
       </c>
       <c r="E1226" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1226" s="1" t="s">
         <v>613</v>
@@ -71146,7 +71146,7 @@
         <v>1155</v>
       </c>
       <c r="E2076" s="1">
-        <v>5591</v>
+        <v>5590</v>
       </c>
       <c r="F2076" s="1" t="s">
         <v>1155</v>
